--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_620_Portugal_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_620_Portugal_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc1c443442ac34635"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Reb338b592fb7490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3c7432111c574d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rba68bbb99edc4102"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R15f57779f6fe4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6848aed690b0421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcca9cd41c92e4826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R11bb692bd3354b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rce3f5b318d7a4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb8195631f7b54535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R483fa8b672734522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1a0dd33ae94a40fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ620CommercialTable" displayName="EEZ620CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ620CommercialTable" displayName="EEZ620CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ620FunctionalTable" displayName="EEZ620FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ620FunctionalTable" displayName="EEZ620FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ620ValidationTable" displayName="EEZ620ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ620ValidationTable" displayName="EEZ620ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -17712,7 +17666,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c66001e766c4eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82d61f5528eb4771"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17722,20 +17676,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -17743,714 +17687,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9116.998411403</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9116.998411403</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$255,A2,'Species'!$U$2:$U$255))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1174496.9116276926</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1174496.9116276926</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>15800.0944865726</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.205179355878875</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1603.9076391944034</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>15800.0944865726</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1808.8442110329577</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$255,A3,'Species'!$U$2:$U$255))</x:f>
-        <x:v>28579909.445810597</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.205179355878875</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1603.9076391944034</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>25341892.24700717</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3238017.1988034286</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1277732999273498</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.12777329992734984</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3563.1982984037004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9566632136637603</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>90.50304963767528</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3563.1982984037004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>119.22673619639762</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$255,A4,'Species'!$U$2:$U$255))</x:f>
-        <x:v>424828.5035392309</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9566632136637603</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>90.50304963767528</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>322480.3124693102</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>102348.19106992072</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3173781068562471</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.31737810685624723</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2272.6173424501</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.418196348772205</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>261.9366981922614</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2272.6173424501</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>416.7359236254435</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$255,A5,'Species'!$U$2:$U$255))</x:f>
-        <x:v>947081.2872531431</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.418196348772205</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>261.9366981922614</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>595281.882935851</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>351799.40431729215</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5909795248299248</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5909795248299248</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>15506.9186895417</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0595278189260204</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.69059846420761</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>15506.9186895417</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.92098022191509</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$255,A6,'Species'!$U$2:$U$255))</x:f>
-        <x:v>1782070.296023667</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0595278189260204</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.69059846420761</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1778497.7848393437</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3572.5111843233462</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0020087239999829</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0020087239999829745</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>22123.0754307498</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1025167846775066</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.662422044816743</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>22123.0754307498</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.793770059797978</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$255,A7,'Species'!$U$2:$U$255))</x:f>
-        <x:v>283037.540076579</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1025167846775066</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.662422044816743</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>280131.7180334699</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2905.822043109103</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0103730561591098</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01037305615910983</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>77927.2213024661</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.37700987636544</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>238.23736467111345</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>77927.2213024661</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>357.336393515451</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$255,A8,'Species'!$U$2:$U$255))</x:f>
-        <x:v>27846232.216903664</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.37700987636544</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>238.23736467111345</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>18565175.83924218</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>9281056.377661485</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4999175045810034</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.49991750458100337</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>47090.93277804871</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5302258132764743</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>339.0203854214815</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>47090.93277804871</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>531.7840807279384</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$255,A9,'Species'!$U$2:$U$255))</x:f>
-        <x:v>25042208.397995777</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5302258132764743</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>339.0203854214815</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>15964786.180271149</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9077422.217724629</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5685902783303332</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5685902783303332</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13.5193801076</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.641780804069816</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>438.30941959960074</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13.5193801076</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>439.5554711580146</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$255,A10,'Species'!$U$2:$U$255))</x:f>
-        <x:v>5942.517492960408</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.641780804069816</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>438.30941959960074</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5925.671648308544</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>16.845844651864354</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0028428582701967</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0028428582701967506</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3102.6986700854004</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.6805376807945414</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>479.22303004527225</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3102.6986700854004</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>499.8415338471078</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$255,A11,'Species'!$U$2:$U$255))</x:f>
-        <x:v>1550857.662320868</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.6805376807945414</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>479.22303004527225</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1486884.657995762</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>63973.00432510604</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.043024860052923</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.04302486005292307</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4802.3628283926</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.049841449111585</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1121.6089060321544</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4802.3628283926</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1295.5302806713141</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$255,A12,'Species'!$U$2:$U$255))</x:f>
-        <x:v>6221606.462952951</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.049841449111585</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1121.6089060321544</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>5386372.918322907</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>835233.5446300441</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1550641883314128</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.15506418833141267</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>7022.950843518501</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.456688404613193</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2862.1237311454183</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>7022.950843518501</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2897.883554772667</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$255,A13,'Species'!$U$2:$U$255))</x:f>
-        <x:v>20351693.755409095</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.456688404613193</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2862.1237311454183</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>20100554.271902036</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>251139.4835070595</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0124941571316828</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.012494157131682677</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc5becb4768a4da7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99a8e3e629b7458c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18460,20 +17940,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -18481,1470 +17951,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8573.338679366701</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.728524940183368</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>535.2108883879722</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8573.338679366701</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>664.0780408501189</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$255,A2,'Species'!$U$2:$U$255))</x:f>
-        <x:v>5693365.953738385</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.728524940183368</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>535.2108883879722</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4588544.211034817</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1104821.7427035682</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2407782712535762</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.24077827125357626</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>55.7760596857</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>55.7760596857</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.62277660168379</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$255,A3,'Species'!$U$2:$U$255))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1763.7938751630725</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1763.7938751630725</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>549.6119668549</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.864319954165887</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>731.6779279715224</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>549.6119668549</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>762.5530944408976</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$255,A4,'Species'!$U$2:$U$255))</x:f>
-        <x:v>419108.306066952</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.864319954165887</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>731.6779279715224</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>402138.94509674626</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>16969.360970205744</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0421977557187934</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.042197755718793334</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10.1367283968</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.32790608354371</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2127.678884325442</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10.1367283968</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2150.3772292447866</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$255,A5,'Species'!$U$2:$U$255))</x:f>
-        <x:v>21797.789923517732</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.32790608354371</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2127.678884325442</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21567.702966013454</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>230.08695750427796</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0106681252921024</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.010668125292102301</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2737.6064074107003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.4474892000098425</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2802.1359375742722</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2737.6064074107003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2846.7055395283323</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$255,A6,'Species'!$U$2:$U$255))</x:f>
-        <x:v>7793159.3250242965</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.4474892000098425</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2802.1359375742722</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7671145.2971391175</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>122014.02788517904</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.015905581651632</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.015905581651631997</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9532.888872831698</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.356357665922701</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2271.7349831788565</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9532.888872831698</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2379.0477161361937</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$255,A7,'Species'!$U$2:$U$255))</x:f>
-        <x:v>22679197.501090385</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.356357665922701</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2271.7349831788565</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>21656197.143168226</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1023000.3579221591</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0472382270607876</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04723822706078754</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>201.36562391950002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.741708138892999</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>551.706548539711</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>201.36562391950002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1105.4911059252147</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$255,A8,'Species'!$U$2:$U$255))</x:f>
-        <x:v>222607.90628208895</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.741708138892999</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>551.706548539711</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>111094.73336717283</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>111513.17291491613</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.0037665111122807</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.0037665111122804</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>6383.1728986032995</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.45755939454604</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2867.8695614613716</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>6383.1728986032995</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2898.321024925214</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$255,A9,'Species'!$U$2:$U$255))</x:f>
-        <x:v>18500484.217754763</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.45755939454604</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2867.8695614613716</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>18306107.261449557</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>194376.95630520582</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0106181480054222</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.010618148005422219</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1207.7295651646</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8192186844384537</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>659.5058989379143</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1207.7295651646</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>659.899213456126</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$255,A10,'Species'!$U$2:$U$255))</x:f>
-        <x:v>796979.7901198285</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8192186844384537</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>659.5058989379143</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>796504.7725477758</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>475.0175720527768</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0005963775590865</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.000596377559086483</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1449.0186513533001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.720438168500555</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>525.3372163236367</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1449.0186513533001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>538.2772077061844</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$255,A11,'Species'!$U$2:$U$255))</x:f>
-        <x:v>779973.7135646355</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.720438168500555</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>525.3372163236367</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>761223.4247029729</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>18750.288861662615</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.024631781226358</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02463178122635798</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2696.2215416799004</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.196623891527958</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1572.620351122295</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2696.2215416799004</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1711.468020687811</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$255,A12,'Species'!$U$2:$U$255))</x:f>
-        <x:v>4614496.945274738</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.196623891527958</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1572.620351122295</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4240132.867580141</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>374364.0776945967</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0882906478136491</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0882906478136492</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>678.4125050268002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.2266790093354074</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>168.5306940569322</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>678.4125050268002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>217.38256728211067</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$255,A13,'Species'!$U$2:$U$255))</x:f>
-        <x:v>147475.05201901364</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.2266790093354074</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>168.5306940569322</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>114333.33032906863</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>33141.721689945014</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2898692935345986</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.28986929353459856</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1334.8700840535</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.005016019795369</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1011.6167690207759</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1334.8700840535</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1759.1029455144678</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$255,A14,'Species'!$U$2:$U$255))</x:f>
-        <x:v>2348173.896737657</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.005016019795369</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1011.6167690207759</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1350376.9614926933</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>997796.9352449637</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.738902516629141</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.7389025166291411</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>13.9934229344</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.064768651793691</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1160.8300761669836</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>13.9934229344</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1175.7405052174108</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$255,A15,'Species'!$U$2:$U$255))</x:f>
-        <x:v>16452.63415061236</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.064768651793691</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1160.8300761669836</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>16243.986210776367</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>208.64793983599338</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0128446267516267</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.012844626751626701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>20243.774984654698</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6756785773335983</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>473.89112717674215</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>20243.774984654698</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>713.1642038897331</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$255,A16,'Species'!$U$2:$U$255))</x:f>
-        <x:v>14437135.670654163</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6756785773335983</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>473.89112717674215</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>9593345.34579035</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4843790.324863812</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.504911493360271</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5049114933602711</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>70168.3424921693</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.267444107595902</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>185.116064002289</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>70168.3424921693</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>210.59415712236674</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$255,A17,'Species'!$U$2:$U$255))</x:f>
-        <x:v>14777042.943811942</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.267444107595902</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>185.116064002289</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>12989287.379714945</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1787755.5640969966</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.137633074997547</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.1376330749975469</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>25936.3280586704</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.684928101452713</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>484.0922182616309</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>25936.3280586704</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>584.2546975486899</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$255,A18,'Species'!$U$2:$U$255))</x:f>
-        <x:v>15153421.505442074</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.684928101452713</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>484.0922182616309</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>12555574.583483132</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2597846.921958942</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2069078483573672</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.20690784835736722</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>396.36398120940004</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.5444536064347285</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>35.031086429844315</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>396.36398120940004</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>39.100879990494434</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$255,A19,'Species'!$U$2:$U$255))</x:f>
-        <x:v>15498.180461823342</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.5444536064347285</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>35.031086429844315</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>13885.060883423681</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1613.119578399661</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1161766298284974</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.11617662982849732</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>22824.9697860347</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.1055692621695052</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>12.751734509899201</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>22824.9697860347</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>12.93842128822102</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$255,A20,'Species'!$U$2:$U$255))</x:f>
-        <x:v>295319.07498263294</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.1055692621695052</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>12.751734509899201</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>291057.9549079853</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>4261.120074647653</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0146401086202739</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.014640108620273783</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2884.7581300387997</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.893162815044167</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>78.19208882643954</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2884.7581300387997</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>96.14347986348409</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$255,A21,'Species'!$U$2:$U$255))</x:f>
-        <x:v>277350.68518640735</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.893162815044167</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>78.19208882643954</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>225565.26394678745</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>51785.4212396199</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2295806558754387</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.22958065587543866</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2.4431820094</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.64</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>436.5158322401661</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2.4431820094</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>436.5158322401661</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$255,A22,'Species'!$U$2:$U$255))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1066.4876281474424</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.64</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>436.5158322401661</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>1066.4876281474424</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>2944.5043071177</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.3218283086212486</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>209.8110265303007</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>2944.5043071177</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>247.57034062756844</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$255,A23,'Species'!$U$2:$U$255))</x:f>
-        <x:v>728971.9342924714</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.3218283086212486</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>209.8110265303007</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>617789.4712992564</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>111182.46299321495</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.1799682062554258</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.17996820625542567</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>24547.297092474902</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.0792678686259856</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>120.02393709003508</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>24547.297092474902</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>120.36024046414472</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$255,A24,'Species'!$U$2:$U$255))</x:f>
-        <x:v>2954518.58079508</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.0792678686259856</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>120.02393709003508</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>2946263.2419576086</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>8255.338837471325</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0028019691926735</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0028019691926734172</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>2071.2517185306</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.386744761850069</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>243.6378519450588</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>2071.2517185306</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>349.7756330094994</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$255,A25,'Species'!$U$2:$U$255))</x:f>
-        <x:v>724473.3809710542</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.386744761850069</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>243.6378519450588</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>504635.3195403069</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>219838.06143074727</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.4356374849683664</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.43563748496836646</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>17.351899696999997</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.977180706322983</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>948.81317445018</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>17.351899696999997</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1417.2461590635826</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$255,A26,'Species'!$U$2:$U$255))</x:f>
-        <x:v>24591.91319802979</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.977180706322983</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>948.81317445018</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>16463.711034251683</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>8128.202163778107</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.4937041318854485</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.49370413188544854</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>881.0598218510999</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.9182190018148058</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>828.3597756530974</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>881.0598218510999</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>891.5828356693711</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$255,A27,'Species'!$U$2:$U$255))</x:f>
-        <x:v>785537.8143603546</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.9182190018148058</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>828.3597756530974</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>729834.516365535</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>55703.297994819586</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.076323189361081</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.07632318936108085</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151569d77a584004"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c6374d19a7418c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20119,7 +18635,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -20218,7 +18734,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>114209964.99740623</x:v>
+        <x:v>91002480.39629517</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20232,7 +18748,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>114209964.9974062</x:v>
+        <x:v>100522142.76751196</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20246,7 +18762,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.4901161193847656e-8</x:v>
+        <x:v>-23207484.60111104</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20260,7 +18776,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-13687822.22989425</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20271,9 +18787,9 @@
         <x:v>EEZ_620</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -20285,47 +18801,19 @@
         <x:v>EEZ_620</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_620</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_620</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb05f7242b7bb4c5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R749957d3951248ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20372,7 +18860,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
